--- a/academias/Programación - Estadisticos 20241.xlsx
+++ b/academias/Programación - Estadisticos 20241.xlsx
@@ -1001,25 +1001,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1036,25 +1036,25 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1068,25 +1068,25 @@
         <v>52</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F4">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>94.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>5.8</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1103,25 +1103,25 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1138,25 +1138,25 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1170,25 +1170,25 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>6.4</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1205,25 +1205,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1240,25 +1240,25 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1272,25 +1272,25 @@
         <v>62</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F10">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1307,25 +1307,25 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1342,25 +1342,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1374,25 +1374,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>5.4</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1403,25 +1403,25 @@
         <v>198</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="F14">
-        <v>198</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1489,19 +1489,19 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H2" s="1">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1524,19 +1524,19 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>5.8</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1591,19 +1591,19 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>10.5</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1658,19 +1658,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>91.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1693,19 +1693,19 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>2.9</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         <v>62</v>
       </c>
       <c r="E10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>93.5</v>
+        <v>95.2</v>
       </c>
       <c r="H10" s="1">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>5.6</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>5.4</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1891,16 +1891,16 @@
         <v>198</v>
       </c>
       <c r="E14">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>93.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="I14" s="2">
         <v>8.300000000000001</v>

--- a/academias/Programación - Estadisticos 20241.xlsx
+++ b/academias/Programación - Estadisticos 20241.xlsx
@@ -1489,19 +1489,19 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1556,16 +1556,16 @@
         <v>52</v>
       </c>
       <c r="E4">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>8.4</v>
@@ -1603,7 +1603,7 @@
         <v>3.6</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1626,19 +1626,19 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1658,19 +1658,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>93.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H7" s="1">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1830,19 +1830,19 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1862,19 +1862,19 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H13" s="1">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="I13" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1891,19 +1891,19 @@
         <v>198</v>
       </c>
       <c r="E14">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="H14" s="1">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>

--- a/academias/Programación - Estadisticos 20241.xlsx
+++ b/academias/Programación - Estadisticos 20241.xlsx
@@ -1693,19 +1693,19 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1728,19 +1728,19 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         <v>62</v>
       </c>
       <c r="E10">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1891,16 +1891,16 @@
         <v>198</v>
       </c>
       <c r="E14">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2">
         <v>8.199999999999999</v>
